--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,16 +3411,16 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45932.44791666666</v>
+        <v>45932.375</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45932.48958333334</v>
+        <v>45932.44791666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.48958333334</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,65 +2858,65 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,65 +2987,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45932.625</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="21">

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,16 +3411,16 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G26" t="n">

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>JS Kabylie</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>JS Kabylie</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,16 +3411,16 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45932.35416666666</v>
+        <v>45932.375</v>
       </c>
     </row>
     <row r="6">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45932.375</v>
+        <v>45932.44791666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45932.44791666666</v>
+        <v>45932.48958333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45932.48958333334</v>
+        <v>45932.5</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,65 +2858,65 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,65 +2987,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.66666666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45932.66666666666</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.8125</v>
       </c>
     </row>
     <row r="24">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.65</v>
+        <v>1.71</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>2.65</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45932.8125</v>
+        <v>45932.85416666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,135 +3715,6 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45932.85416666666</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="3" t="n">
         <v>45932.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45932.375</v>
+        <v>45932.44791666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45932.44791666666</v>
+        <v>45932.48958333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45932.48958333334</v>
+        <v>45932.5</v>
       </c>
     </row>
     <row r="9">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,65 +2729,65 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,65 +2858,65 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.625</v>
       </c>
     </row>
     <row r="20">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Y22" t="n">
         <v>2.56</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AA23" t="n">
         <v>3.8</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
         <v>3.72</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AK23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,65 +2471,65 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.625</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,65 +2729,65 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>3.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="O18" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.66666666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45932.625</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45932.66666666666</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.8125</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.31</v>
+        <v>1.66</v>
       </c>
       <c r="M22" t="n">
-        <v>2.87</v>
+        <v>3.29</v>
       </c>
       <c r="N22" t="n">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.85416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3457,264 +3457,6 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45932.8125</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
-        <v>45932.85416666666</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Criciúma EC B</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="3" t="n">
         <v>45932.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2484,52 +2484,52 @@
         <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
         <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.02</v>
+        <v>3.42</v>
       </c>
       <c r="M18" t="n">
-        <v>3.13</v>
+        <v>3.52</v>
       </c>
       <c r="N18" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2871,28 +2871,28 @@
         <v>2.96</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W19" t="n">
         <v>1.55</v>
@@ -2907,16 +2907,16 @@
         <v>1.51</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3000,34 +3000,34 @@
         <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y20" t="n">
         <v>2.17</v>
@@ -3036,16 +3036,16 @@
         <v>1.62</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3129,34 +3129,34 @@
         <v>2.57</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y21" t="n">
         <v>2.2</v>
@@ -3171,10 +3171,10 @@
         <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3258,34 +3258,34 @@
         <v>4.7</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y22" t="n">
         <v>2.18</v>
@@ -3294,16 +3294,16 @@
         <v>1.68</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK23"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.625</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.66666666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.8125</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.85416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,65 +2471,65 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.47</v>
+        <v>2.69</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>2.76</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>4.11</v>
       </c>
       <c r="R16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.28</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.57</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.31</v>
+        <v>1.49</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.48</v>
+        <v>5.28</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.47</v>
+        <v>2.09</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.42</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,909 +2554,6 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45932.58333333334</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Kenya Kenyan Premier League</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TransMara Sugar</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Nairobi United</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="n">
-        <v>45932.625</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>England EFL League One</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Rotherham United</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Bradford City</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
-        <v>45932.66666666666</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Vitória</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3" t="n">
-        <v>45932.79166666666</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Paysandu</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
-        <v>45932.79166666666</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="3" t="n">
-        <v>45932.8125</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
-        <v>45932.85416666666</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Criciúma EC B</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="n">
         <v>45932.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45932.44791666666</v>
+        <v>45932.375</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45932.48958333334</v>
+        <v>45932.44791666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.48958333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45932.625</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="11">

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1719,7 +1719,7 @@
         <v>2.62</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
         <v>3.6</v>
@@ -1734,7 +1734,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
         <v>4.6</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="n">
         <v>1.36</v>
@@ -1839,13 +1839,13 @@
         <v>2.13</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>4.13</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="R11" t="n">
         <v>1.35</v>
@@ -1854,16 +1854,16 @@
         <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="U11" t="n">
         <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X11" t="n">
         <v>3.4</v>
@@ -1878,10 +1878,10 @@
         <v>3.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AD11" t="n">
         <v>2.02</v>
@@ -1900,7 +1900,7 @@
         <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>2.78</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P12" t="n">
         <v>1.94</v>
@@ -1995,7 +1995,7 @@
         <v>1.37</v>
       </c>
       <c r="X12" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="Y12" t="n">
         <v>2.17</v>
@@ -2004,10 +2004,10 @@
         <v>1.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC12" t="n">
         <v>1.94</v>
@@ -2100,16 +2100,16 @@
         <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
         <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="T13" t="n">
         <v>3.42</v>
@@ -2136,7 +2136,7 @@
         <v>4.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AC13" t="n">
         <v>2.12</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
         <v>1.56</v>
@@ -2229,7 +2229,7 @@
         <v>3.46</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
         <v>3.32</v>
@@ -2244,7 +2244,7 @@
         <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
         <v>1.03</v>
@@ -2253,7 +2253,7 @@
         <v>1.34</v>
       </c>
       <c r="X14" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Y14" t="n">
         <v>2.2</v>
@@ -2271,7 +2271,7 @@
         <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2355,13 +2355,13 @@
         <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="R15" t="n">
         <v>1.41</v>
@@ -2370,19 +2370,19 @@
         <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.93</v>
+        <v>3.22</v>
       </c>
       <c r="U15" t="n">
         <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="X15" t="n">
-        <v>3.09</v>
+        <v>2.97</v>
       </c>
       <c r="Y15" t="n">
         <v>2.18</v>
@@ -2391,16 +2391,16 @@
         <v>1.68</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2484,22 +2484,22 @@
         <v>2.76</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
         <v>1.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.11</v>
+        <v>3.96</v>
       </c>
       <c r="R16" t="n">
         <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="U16" t="n">
         <v>1.28</v>
@@ -2520,16 +2520,16 @@
         <v>1.49</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.28</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AC16" t="n">
         <v>2.09</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1710,19 +1710,19 @@
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R10" t="n">
         <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="T10" t="n">
         <v>2.27</v>
@@ -1737,25 +1737,25 @@
         <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y10" t="n">
         <v>1.55</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="M12" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="O12" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
         <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X12" t="n">
         <v>2.5</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.67</v>
-      </c>
       <c r="Y12" t="n">
-        <v>2.17</v>
+        <v>2.56</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="P13" t="n">
         <v>1.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="X13" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.56</v>
+        <v>2.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>4.13</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
         <v>1.35</v>
@@ -1860,28 +1860,28 @@
         <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AD11" t="n">
         <v>2.02</v>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1959,16 +1959,16 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="P12" t="n">
         <v>1.94</v>
@@ -1983,28 +1983,28 @@
         <v>2.32</v>
       </c>
       <c r="T12" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
         <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AB12" t="n">
         <v>1.12</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
         <v>1.56</v>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="M13" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="O13" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         <v>3.46</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>3.32</v>
@@ -2241,7 +2241,7 @@
         <v>2.51</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
         <v>1.31</v>
@@ -2250,28 +2250,28 @@
         <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="X14" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC14" t="n">
         <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AH14" t="n">
         <v>1.46</v>
@@ -2346,31 +2346,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="M15" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>6.19</v>
       </c>
       <c r="O15" t="n">
         <v>2.14</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.4</v>
+        <v>6.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
         <v>1.33</v>
@@ -2382,22 +2382,22 @@
         <v>1.32</v>
       </c>
       <c r="X15" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AA15" t="n">
         <v>3.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AD15" t="n">
         <v>1.7</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="M16" t="n">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="P16" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.96</v>
+        <v>4.11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
         <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="V16" t="n">
         <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Y16" t="n">
         <v>2.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AA16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>4.13</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="R11" t="n">
         <v>1.35</v>
@@ -1854,7 +1854,7 @@
         <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
         <v>1.37</v>
@@ -1863,22 +1863,22 @@
         <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AA11" t="n">
         <v>3.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
         <v>1.72</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
         <v>1.31</v>
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="O12" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="P12" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
         <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X12" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AB12" t="n">
         <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2088,58 +2088,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.54</v>
+        <v>3.19</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.4</v>
+        <v>4.76</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AD13" t="n">
         <v>1.77</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         <v>3.46</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
         <v>3.32</v>
@@ -2241,7 +2241,7 @@
         <v>2.51</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
         <v>1.31</v>
@@ -2250,25 +2250,25 @@
         <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="X14" t="n">
         <v>2.88</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD14" t="n">
         <v>1.87</v>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
         <v>1.46</v>
@@ -2346,31 +2346,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N15" t="n">
-        <v>6.19</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.54</v>
+        <v>6.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="U15" t="n">
         <v>1.33</v>
@@ -2382,25 +2382,25 @@
         <v>1.32</v>
       </c>
       <c r="X15" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AA15" t="n">
         <v>3.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="O16" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="P16" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.11</v>
+        <v>4.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="T16" t="n">
         <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Z16" t="n">
         <v>1.48</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK16"/>
+  <dimension ref="A1:AK18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.5</v>
       </c>
     </row>
     <row r="10">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45932.66666666666</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>2.87</v>
+        <v>3.47</v>
       </c>
       <c r="N12" t="n">
-        <v>2.96</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.92</v>
+        <v>2.67</v>
       </c>
       <c r="R12" t="n">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2.3</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AA12" t="n">
-        <v>4.65</v>
+        <v>2.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.08</v>
+        <v>1.43</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>2.59</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,11 +2026,11 @@
         </is>
       </c>
       <c r="AG12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.38</v>
       </c>
-      <c r="AH12" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,77 +2088,77 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>3.02</v>
       </c>
       <c r="M13" t="n">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>2.13</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>4.13</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.19</v>
+        <v>2.67</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="T13" t="n">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
         <v>1.3</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.66666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
-        <v>3.46</v>
+        <v>3.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S14" t="n">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
         <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45932.8125</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,62 +2346,62 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>2.31</v>
       </c>
       <c r="M15" t="n">
-        <v>3.29</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>2.96</v>
       </c>
       <c r="O15" t="n">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.35</v>
+        <v>3.92</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.93</v>
+        <v>3.42</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="X15" t="n">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="Z15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.68</v>
       </c>
-      <c r="AA15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AE15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.33</v>
+        <v>1.55</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45932.85416666666</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,85 +2475,343 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="M16" t="n">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>2.57</v>
       </c>
       <c r="O16" t="n">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.04</v>
+        <v>3.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
         <v>1.28</v>
       </c>
       <c r="V16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <v>45932.8125</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>45932.85416666666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Criciúma EC B</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.07</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W18" t="n">
         <v>1.5</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X18" t="n">
         <v>2.4</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y18" t="n">
         <v>2.58</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z18" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA18" t="n">
         <v>4.8</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AB18" t="n">
         <v>1.12</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AC18" t="n">
         <v>2.11</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AD18" t="n">
         <v>1.66</v>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.37</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AH18" t="n">
         <v>1.53</v>
       </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="3" t="n">
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
         <v>45932.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AK17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45932.375</v>
+        <v>45932.44791666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45932.44791666666</v>
+        <v>45932.48958333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45932.48958333334</v>
+        <v>45932.5</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="M12" t="n">
-        <v>3.47</v>
+        <v>3.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>4.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
         <v>2.67</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7</v>
+        <v>2.84</v>
       </c>
       <c r="T12" t="n">
-        <v>2.17</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.33</v>
+        <v>3.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.59</v>
+        <v>2.02</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.66666666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.02</v>
+        <v>2.31</v>
       </c>
       <c r="M13" t="n">
-        <v>3.13</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>2.13</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>4.13</v>
+        <v>3.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.67</v>
+        <v>3.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.91</v>
+        <v>2.56</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.2</v>
+        <v>4.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45932.66666666666</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="O14" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
         <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.54</v>
+        <v>3.19</v>
       </c>
       <c r="R14" t="n">
         <v>1.49</v>
@@ -2247,19 +2247,19 @@
         <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="X14" t="n">
         <v>2.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AA14" t="n">
         <v>4.4</v>
@@ -2271,7 +2271,7 @@
         <v>1.96</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.31</v>
+        <v>2.57</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="N15" t="n">
-        <v>2.96</v>
+        <v>2.57</v>
       </c>
       <c r="O15" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.92</v>
+        <v>3.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="T15" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.8125</v>
       </c>
     </row>
     <row r="16">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.57</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>2.94</v>
+        <v>3.29</v>
       </c>
       <c r="N16" t="n">
-        <v>2.57</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>2.14</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.54</v>
+        <v>6.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="X16" t="n">
-        <v>2.67</v>
+        <v>2.97</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z16" t="n">
         <v>1.68</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45932.8125</v>
+        <v>45932.85416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Criciúma EC B</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,62 +2604,62 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.66</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.33</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,135 +2683,6 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45932.85416666666</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Criciúma EC B</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
         <v>45932.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1839,52 +1839,52 @@
         <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="U11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1968,13 +1968,13 @@
         <v>2.13</v>
       </c>
       <c r="O12" t="n">
-        <v>4.13</v>
+        <v>4.05</v>
       </c>
       <c r="P12" t="n">
         <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="R12" t="n">
         <v>1.35</v>
@@ -2007,13 +2007,13 @@
         <v>3.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AC12" t="n">
         <v>1.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>3.15</v>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
         <v>3.92</v>
@@ -2112,10 +2112,10 @@
         <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V13" t="n">
         <v>1.07</v>
@@ -2127,19 +2127,19 @@
         <v>2.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.65</v>
+        <v>5.1</v>
       </c>
       <c r="AB13" t="n">
         <v>1.12</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AD13" t="n">
         <v>1.68</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
         <v>1.55</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="M14" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="O14" t="n">
         <v>3.4</v>
@@ -2232,13 +2232,13 @@
         <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T14" t="n">
         <v>3.34</v>
@@ -2253,25 +2253,25 @@
         <v>1.47</v>
       </c>
       <c r="X14" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="Y14" t="n">
         <v>2.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AA14" t="n">
         <v>4.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2355,19 +2355,19 @@
         <v>2.57</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.42</v>
+        <v>2.57</v>
       </c>
       <c r="T15" t="n">
         <v>3.2</v>
@@ -2376,10 +2376,10 @@
         <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
         <v>2.67</v>
@@ -2397,10 +2397,10 @@
         <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2484,25 +2484,25 @@
         <v>4.7</v>
       </c>
       <c r="O16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.14</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q16" t="n">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>3.21</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
         <v>1.02</v>
@@ -2526,10 +2526,10 @@
         <v>1.23</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Criciúma EC B</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2607,22 +2607,22 @@
         <v>2.45</v>
       </c>
       <c r="M17" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.04</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
         <v>2.31</v>
@@ -2637,10 +2637,10 @@
         <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X17" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="Y17" t="n">
         <v>2.58</v>
@@ -2655,10 +2655,10 @@
         <v>1.12</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1959,34 +1959,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P12" t="n">
         <v>2.13</v>
       </c>
-      <c r="O12" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q12" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="R12" t="n">
         <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
         <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
@@ -1995,19 +1995,19 @@
         <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Y12" t="n">
         <v>1.91</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
         <v>3.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
         <v>1.72</v>
@@ -2029,7 +2029,7 @@
         <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="O13" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.92</v>
+        <v>3.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="T13" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,31 +2217,31 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
         <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T14" t="n">
         <v>3.4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.34</v>
       </c>
       <c r="U14" t="n">
         <v>1.28</v>
@@ -2253,25 +2253,25 @@
         <v>1.47</v>
       </c>
       <c r="X14" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2358,10 +2358,10 @@
         <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="R15" t="n">
         <v>1.51</v>
@@ -2370,7 +2370,7 @@
         <v>2.57</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="U15" t="n">
         <v>1.28</v>
@@ -2379,28 +2379,28 @@
         <v>1.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X15" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC15" t="n">
         <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AH15" t="n">
         <v>1.46</v>
@@ -2475,58 +2475,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="M16" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="P16" t="n">
         <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.15</v>
+        <v>6.35</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
         <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="X16" t="n">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.55</v>
+        <v>3.86</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" t="n">
         <v>1.7</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK17"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.47</v>
+        <v>2.88</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45932.66666666666</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.56</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>3.47</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>2.31</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.05</v>
+        <v>2.64</v>
       </c>
       <c r="R14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.55</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.55</v>
-      </c>
       <c r="Z14" t="n">
-        <v>1.49</v>
+        <v>2.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.65</v>
+        <v>2.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.17</v>
+        <v>1.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.66</v>
+        <v>2.59</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,62 +2346,62 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.57</v>
+        <v>3.02</v>
       </c>
       <c r="M15" t="n">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>4.13</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.54</v>
+        <v>2.67</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="T15" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.28</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AC15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD15" t="n">
         <v>2</v>
       </c>
-      <c r="AD15" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45932.8125</v>
+        <v>45932.66666666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.73</v>
+        <v>2.31</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>2.96</v>
       </c>
       <c r="O16" t="n">
-        <v>2.13</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.35</v>
+        <v>4.05</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>3.13</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.86</v>
+        <v>4.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.24</v>
+        <v>1.55</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45932.85416666666</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,126 +2563,513 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>45932.79166666666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
+        <v>45932.8125</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
+        <v>45932.85416666666</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="L20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.53</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="n">
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
         <v>45932.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1101,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45932.375</v>
+        <v>45932.35416666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45932.44791666666</v>
+        <v>45932.375</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45932.48958333334</v>
+        <v>45932.44791666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.48958333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.5</v>
       </c>
     </row>
     <row r="10">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.71</v>
+        <v>2.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>2.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="M14" t="n">
-        <v>3.47</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="X14" t="n">
-        <v>4.98</v>
+        <v>2.43</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.13</v>
+        <v>3.47</v>
       </c>
       <c r="N15" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>4.13</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S15" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.2</v>
+        <v>2.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45932.66666666666</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.31</v>
+        <v>3.02</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>3.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.96</v>
+        <v>2.13</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X16" t="n">
         <v>3.4</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Y16" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.65</v>
+        <v>3.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.17</v>
+        <v>1.72</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.66666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="M17" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="N17" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.19</v>
+        <v>3.92</v>
       </c>
       <c r="R17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z17" t="n">
         <v>1.45</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.17</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,31 +2733,31 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="M18" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="N18" t="n">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="T18" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
         <v>1.28</v>
@@ -2766,28 +2766,28 @@
         <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="X18" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45932.8125</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>2.57</v>
       </c>
       <c r="M19" t="n">
-        <v>3.29</v>
+        <v>2.94</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>2.57</v>
       </c>
       <c r="O19" t="n">
-        <v>2.14</v>
+        <v>3.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.35</v>
+        <v>3.55</v>
       </c>
       <c r="R19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.41</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X19" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
         <v>1.68</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.33</v>
+        <v>1.46</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45932.85416666666</v>
+        <v>45932.8125</v>
       </c>
     </row>
     <row r="20">
@@ -2950,126 +2950,255 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
+        <v>45932.85416666666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>2.6</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>2.69</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>2.76</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="R20" t="n">
+      <c r="O21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.57</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>2.31</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="T21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.11</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AC21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.66</v>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.37</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AH21" t="n">
         <v>1.53</v>
       </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="3" t="n">
         <v>45932.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK21"/>
+  <dimension ref="A1:AK19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.43</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45932.5</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,49 +1959,49 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
         <v>2.35</v>
       </c>
-      <c r="M12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
+      <c r="Z12" t="n">
         <v>1.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>3.47</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.04</v>
+        <v>3.02</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.13</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>2.13</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>2.43</v>
+        <v>3.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.66666666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,78 +2346,78 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="M15" t="n">
-        <v>3.47</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>2.96</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.64</v>
+        <v>3.92</v>
       </c>
       <c r="R15" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="U15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.55</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.15</v>
-      </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.02</v>
+        <v>2.36</v>
       </c>
       <c r="M16" t="n">
-        <v>3.13</v>
+        <v>2.97</v>
       </c>
       <c r="N16" t="n">
-        <v>2.13</v>
+        <v>2.78</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.65</v>
+        <v>3.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45932.66666666666</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.31</v>
+        <v>2.57</v>
       </c>
       <c r="M17" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="N17" t="n">
-        <v>2.96</v>
+        <v>2.57</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.92</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="T17" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.8125</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.36</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>2.97</v>
+        <v>3.29</v>
       </c>
       <c r="N18" t="n">
-        <v>2.78</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.45</v>
+        <v>2.14</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.44</v>
+        <v>6.35</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="X18" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.85416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="N19" t="n">
-        <v>2.57</v>
+        <v>2.76</v>
       </c>
       <c r="O19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.55</v>
+        <v>4.07</v>
       </c>
       <c r="R19" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="U19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.8</v>
+        <v>4.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>1.37</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,264 +2941,6 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45932.8125</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
-        <v>45932.85416666666</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="3" t="n">
         <v>45932.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45932.33333333334</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.18</v>
+        <v>1.81</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45932.35416666666</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.43</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2100,25 +2100,25 @@
         <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
         <v>1.15</v>
@@ -2139,7 +2139,7 @@
         <v>1.54</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AD13" t="n">
         <v>2.4</v>
@@ -2158,13 +2158,13 @@
         <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45932.58333333334</v>
@@ -2238,7 +2238,7 @@
         <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
         <v>2.75</v>
@@ -2253,7 +2253,7 @@
         <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Y14" t="n">
         <v>1.91</v>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45932.66666666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.92</v>
+        <v>3.48</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="Z15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.45</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="M16" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="O16" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.44</v>
+        <v>3.98</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="S16" t="n">
         <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.17</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2742,13 +2742,13 @@
         <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="P18" t="n">
         <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="R18" t="n">
         <v>1.41</v>
@@ -2757,10 +2757,10 @@
         <v>2.6</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
@@ -2784,7 +2784,7 @@
         <v>1.23</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
         <v>1.67</v>
@@ -2874,22 +2874,22 @@
         <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.07</v>
+        <v>3.64</v>
       </c>
       <c r="R19" t="n">
         <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="T19" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V19" t="n">
         <v>1.12</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
         <v>1.53</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK19"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="O3" t="n">
         <v>2.75</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -871,10 +871,10 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45932.33333333334</v>
@@ -927,46 +927,46 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P4" t="n">
         <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T4" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="U4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V4" t="n">
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
         <v>1.76</v>
@@ -975,13 +975,13 @@
         <v>3.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AI4" t="n">
         <v>1.72</v>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.47</v>
+        <v>4.75</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="O5" t="n">
-        <v>3.98</v>
+        <v>4.54</v>
       </c>
       <c r="P5" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="R5" t="n">
         <v>1.17</v>
@@ -1080,10 +1080,10 @@
         <v>4.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1092,25 +1092,25 @@
         <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AI5" t="n">
         <v>2.38</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.66666666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,62 +1959,62 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.7</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
       <c r="AE12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M13" t="n">
         <v>3</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.47</v>
-      </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.55</v>
+        <v>3.19</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>2.48</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.3</v>
+        <v>1.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.33</v>
+        <v>4.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.54</v>
+        <v>1.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,62 +2217,62 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.02</v>
+        <v>2.57</v>
       </c>
       <c r="M14" t="n">
-        <v>3.13</v>
+        <v>2.94</v>
       </c>
       <c r="N14" t="n">
-        <v>2.13</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.65</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.41</v>
       </c>
-      <c r="V14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X14" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="Z14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.79</v>
       </c>
-      <c r="AA14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2</v>
-      </c>
       <c r="AE14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2284,19 +2284,19 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45932.66666666666</v>
+        <v>45932.8125</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,86 +2346,86 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.36</v>
+        <v>1.73</v>
       </c>
       <c r="M15" t="n">
-        <v>2.97</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>2.78</v>
+        <v>5.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>2.14</v>
       </c>
       <c r="P15" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.48</v>
+        <v>6.2</v>
       </c>
       <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AI15" t="n">
         <v>1.51</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="AJ15" t="n">
         <v>3.3</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
       <c r="AK15" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.85416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S16" t="n">
         <v>2.31</v>
       </c>
-      <c r="M16" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.44</v>
-      </c>
       <c r="T16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.11</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AC16" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,405 +2542,18 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45932.79166666666</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="n">
-        <v>45932.8125</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
-        <v>45932.85416666666</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3" t="n">
         <v>45932.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="N3" t="n">
-        <v>3.32</v>
+        <v>3.39</v>
       </c>
       <c r="O3" t="n">
         <v>2.75</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="O4" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>3.96</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
         <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="X4" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Z4" t="n">
         <v>1.76</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.45</v>
+        <v>2.97</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AI4" t="n">
         <v>1.72</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.69</v>
+        <v>3.19</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W12" t="n">
         <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45932.79166666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.19</v>
+        <v>4.13</v>
       </c>
       <c r="R13" t="n">
         <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="T13" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W13" t="n">
         <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45932.79166666666</v>
@@ -2226,19 +2226,19 @@
         <v>2.57</v>
       </c>
       <c r="O14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.25</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.55</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
         <v>3.2</v>
@@ -2250,7 +2250,7 @@
         <v>1.09</v>
       </c>
       <c r="W14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
         <v>2.8</v>
@@ -2259,19 +2259,19 @@
         <v>2.41</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AA14" t="n">
         <v>4.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" t="n">
         <v>2.05</v>
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N15" t="n">
-        <v>5.75</v>
+        <v>5.96</v>
       </c>
       <c r="O15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.2</v>
+        <v>5.03</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.8</v>
       </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="X15" t="n">
-        <v>3.19</v>
+        <v>3.05</v>
       </c>
       <c r="Y15" t="n">
         <v>2.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AA15" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="AI15" t="n">
         <v>1.51</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK16"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="M3" t="n">
-        <v>3.17</v>
+        <v>3.47</v>
       </c>
       <c r="N3" t="n">
-        <v>3.39</v>
+        <v>3.74</v>
       </c>
       <c r="O3" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Z3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.72</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.8</v>
       </c>
       <c r="AJ3" t="n">
         <v>2.4</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="M4" t="n">
-        <v>3.47</v>
+        <v>3.17</v>
       </c>
       <c r="N4" t="n">
-        <v>3.74</v>
+        <v>3.39</v>
       </c>
       <c r="O4" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AJ4" t="n">
         <v>2.4</v>
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45932.35416666666</v>
+        <v>45932.375</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45932.375</v>
+        <v>45932.44791666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45932.44791666666</v>
+        <v>45932.48958333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45932.48958333334</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,86 +1701,86 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T10" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="Z10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI10" t="n">
         <v>2.3</v>
       </c>
-      <c r="AA10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.66666666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.5</v>
+        <v>2.31</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>2.96</v>
       </c>
       <c r="O11" t="n">
-        <v>3.59</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.63</v>
+        <v>4.18</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>2.84</v>
+        <v>2.47</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="X11" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.89</v>
+        <v>1.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.2</v>
+        <v>4.65</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.72</v>
+        <v>2.19</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45932.66666666666</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="12">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
         <v>3.4</v>
@@ -1974,46 +1974,46 @@
         <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.19</v>
+        <v>3.59</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
         <v>1.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="X12" t="n">
         <v>2.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AA12" t="n">
         <v>4.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AI12" t="n">
         <v>2.05</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>2.57</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.13</v>
+        <v>3.35</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.8125</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,86 +2217,86 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.57</v>
+        <v>1.66</v>
       </c>
       <c r="M14" t="n">
-        <v>2.94</v>
+        <v>3.29</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>5.03</v>
       </c>
       <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AI14" t="n">
         <v>1.51</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45932.8125</v>
+        <v>45932.85416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>2.69</v>
       </c>
       <c r="N15" t="n">
-        <v>5.96</v>
+        <v>2.76</v>
       </c>
       <c r="O15" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.03</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="S15" t="n">
-        <v>2.87</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W15" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.48</v>
+        <v>4.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,147 +2413,18 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.37</v>
+        <v>1.55</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45932.85416666666</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45932</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AK16" s="3" t="n">
         <v>45932.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK15"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,7 +665,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45932.375</v>
+        <v>45932.35416666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45932.44791666666</v>
+        <v>45932.375</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45932.48958333334</v>
+        <v>45932.44791666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45932.54166666666</v>
+        <v>45932.48958333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,86 +1701,86 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.13</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>3.59</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.35</v>
       </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AI10" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45932.66666666666</v>
+        <v>45932.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.31</v>
+        <v>3.02</v>
       </c>
       <c r="M11" t="n">
-        <v>2.87</v>
+        <v>3.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.96</v>
+        <v>2.13</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.59</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.18</v>
+        <v>2.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X11" t="n">
         <v>3.4</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Y11" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.65</v>
+        <v>3.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45932.79166666666</v>
+        <v>45932.66666666666</v>
       </c>
     </row>
     <row r="12">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="M12" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="O12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T12" t="n">
         <v>3.4</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
         <v>1.1</v>
       </c>
       <c r="W12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.4</v>
       </c>
-      <c r="X12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45932.79166666666</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,31 +2088,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>3.59</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
         <v>1.3</v>
@@ -2121,28 +2121,28 @@
         <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AI13" t="n">
         <v>2.05</v>
@@ -2167,7 +2167,7 @@
         <v>2.05</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45932.8125</v>
+        <v>45932.79166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.66</v>
+        <v>2.57</v>
       </c>
       <c r="M14" t="n">
-        <v>3.29</v>
+        <v>2.94</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>2.57</v>
       </c>
       <c r="O14" t="n">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.03</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
-        <v>3.26</v>
+        <v>2.82</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z14" t="n">
         <v>1.68</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,19 +2284,19 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.37</v>
+        <v>1.49</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45932.85416666666</v>
+        <v>45932.8125</v>
       </c>
     </row>
     <row r="15">
@@ -2305,126 +2305,255 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <v>45932.85416666666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Criciúma</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>2.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>2.69</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N16" t="n">
         <v>2.76</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O16" t="n">
         <v>3.2</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P16" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q16" t="n">
         <v>3.8</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>1.53</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>2.4</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>3.5</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>1.25</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V16" t="n">
         <v>1.12</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W16" t="n">
         <v>1.5</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X16" t="n">
         <v>2.4</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y16" t="n">
         <v>2.56</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z16" t="n">
         <v>1.45</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA16" t="n">
         <v>4.85</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AB16" t="n">
         <v>1.14</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AC16" t="n">
         <v>2.23</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AD16" t="n">
         <v>1.67</v>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.33</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AH16" t="n">
         <v>1.55</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AI16" t="n">
         <v>1.95</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AJ16" t="n">
         <v>2.3</v>
       </c>
-      <c r="AK15" s="3" t="n">
+      <c r="AK16" s="3" t="n">
         <v>45932.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,106 +772,106 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="M3" t="n">
-        <v>3.47</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AA3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AJ3" t="n">
         <v>2.4</v>
@@ -901,106 +901,106 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>3.39</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Z4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.72</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.8</v>
       </c>
       <c r="AJ4" t="n">
         <v>2.4</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1052,38 +1052,38 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="N5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O5" t="n">
-        <v>4.33</v>
+        <v>4.47</v>
       </c>
       <c r="P5" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="R5" t="n">
         <v>1.16</v>
       </c>
       <c r="S5" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1092,25 +1092,25 @@
         <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '76']</t>
         </is>
       </c>
       <c r="AG5" t="n">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1310,65 +1310,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="N7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45932.44791666666</v>
@@ -1713,31 +1713,31 @@
         <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="U10" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y10" t="n">
         <v>1.55</v>
@@ -1752,7 +1752,7 @@
         <v>1.54</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AD10" t="n">
         <v>2.45</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AI10" t="n">
         <v>2.15</v>
@@ -1839,25 +1839,25 @@
         <v>2.13</v>
       </c>
       <c r="O11" t="n">
-        <v>3.59</v>
+        <v>4.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="R11" t="n">
         <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
         <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
         <v>1.05</v>
@@ -1866,7 +1866,7 @@
         <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="Y11" t="n">
         <v>1.91</v>
@@ -1878,13 +1878,13 @@
         <v>3.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
         <v>1.72</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AI11" t="n">
         <v>2.3</v>
@@ -1968,28 +1968,28 @@
         <v>2.96</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P12" t="n">
         <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.18</v>
+        <v>3.85</v>
       </c>
       <c r="R12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="U12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
         <v>1.55</v>
@@ -2007,13 +2007,13 @@
         <v>4.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2097,31 +2097,31 @@
         <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P13" t="n">
         <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.59</v>
+        <v>3.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
         <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
         <v>2.6</v>
@@ -2136,13 +2136,13 @@
         <v>4.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" t="n">
         <v>2.05</v>
@@ -2226,34 +2226,34 @@
         <v>2.57</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X14" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="Y14" t="n">
         <v>2.2</v>
@@ -2268,10 +2268,10 @@
         <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" t="n">
         <v>2.05</v>
@@ -2355,13 +2355,13 @@
         <v>4.7</v>
       </c>
       <c r="O15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.16</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.04</v>
-      </c>
       <c r="Q15" t="n">
-        <v>5.03</v>
+        <v>5.2</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
@@ -2370,19 +2370,19 @@
         <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="X15" t="n">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="Y15" t="n">
         <v>2.18</v>
@@ -2394,13 +2394,13 @@
         <v>3.48</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AI15" t="n">
         <v>1.51</v>
@@ -2484,25 +2484,25 @@
         <v>2.76</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>4.07</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="T16" t="n">
         <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V16" t="n">
         <v>1.12</v>
@@ -2523,13 +2523,13 @@
         <v>4.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" t="n">
         <v>1.95</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -790,7 +790,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AJ3" t="n">
         <v>2.4</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -919,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,80 +927,80 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AJ4" t="n">
         <v>2.4</v>
@@ -1426,20 +1426,20 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '85']</t>
         </is>
       </c>
       <c r="AG8" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1713,49 +1713,49 @@
         <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.49</v>
+        <v>2.72</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA10" t="n">
         <v>2.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AI10" t="n">
         <v>2.15</v>
@@ -1780,7 +1780,7 @@
         <v>1.83</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45932.58333333334</v>
+        <v>45932.59375</v>
       </c>
     </row>
     <row r="11">
@@ -1830,34 +1830,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="P11" t="n">
         <v>2.13</v>
       </c>
-      <c r="O11" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q11" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
         <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
         <v>1.05</v>
@@ -1866,13 +1866,13 @@
         <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AA11" t="n">
         <v>3.2</v>
@@ -1884,7 +1884,7 @@
         <v>1.72</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.31</v>
       </c>
       <c r="AI11" t="n">
         <v>2.3</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="M12" t="n">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="N12" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
         <v>3.08</v>
@@ -1980,10 +1980,10 @@
         <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="T12" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="U12" t="n">
         <v>1.25</v>
@@ -1992,28 +1992,28 @@
         <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
         <v>4.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI12" t="n">
         <v>1.97</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="M13" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
         <v>3.42</v>
@@ -2103,46 +2103,46 @@
         <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AA13" t="n">
         <v>4.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="O14" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
         <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="AB14" t="n">
         <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" t="n">
         <v>2.05</v>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="O15" t="n">
         <v>2.14</v>
@@ -2367,10 +2367,10 @@
         <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U15" t="n">
         <v>1.36</v>
@@ -2379,28 +2379,28 @@
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X15" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.48</v>
+        <v>3.32</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AI15" t="n">
         <v>1.51</v>
@@ -2478,58 +2478,58 @@
         <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>3.17</v>
       </c>
       <c r="O16" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.07</v>
+        <v>3.61</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AI16" t="n">
         <v>1.95</v>

--- a/jogos_2025-10-02.xlsx
+++ b/jogos_2025-10-02.xlsx
@@ -1684,20 +1684,20 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+7']</t>
         </is>
       </c>
       <c r="AG10" t="n">
@@ -1813,20 +1813,20 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '50']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56', '81']</t>
         </is>
       </c>
       <c r="AG11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,58 +1959,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="M12" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="O12" t="n">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="R12" t="n">
         <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
         <v>1.75</v>
@@ -2029,13 +2029,13 @@
         <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45932.79166666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T13" t="n">
         <v>3.42</v>
       </c>
-      <c r="P13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45932.79166666666</v>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="M14" t="n">
         <v>3.1</v>
@@ -2226,52 +2226,52 @@
         <v>2.74</v>
       </c>
       <c r="O14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.25</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.3</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U14" t="n">
         <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X14" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.37</v>
+        <v>2.56</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.05</v>
+        <v>4.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC14" t="n">
         <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" t="n">
         <v>2.05</v>
@@ -2346,16 +2346,16 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>5.3</v>
+        <v>6.05</v>
       </c>
       <c r="O15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="P15" t="n">
         <v>2.16</v>
@@ -2364,43 +2364,43 @@
         <v>5.2</v>
       </c>
       <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.36</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X15" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="AB15" t="n">
         <v>1.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH15" t="n">
         <v>2.25</v>
